--- a/app/templates/report/mf.xlsx
+++ b/app/templates/report/mf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820DADF3-8EDF-4A1C-ADB8-43A6ED98081F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E00C1A1-457E-4AB4-8756-64CE86590821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,9 +95,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -242,7 +241,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -319,9 +318,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -711,11 +707,11 @@
   <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.77734375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="6" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.44140625" style="8" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -740,12 +736,12 @@
         <v>6</v>
       </c>
       <c r="G1" s="12">
-        <f>SUBTOTAL(9,G3:G3)</f>
+        <f>SUBTOTAL(9,G3:G99999)</f>
         <v>0</v>
       </c>
       <c r="H1" s="13"/>
       <c r="I1" s="12">
-        <f>SUBTOTAL(9,I3:I3)</f>
+        <f>SUBTOTAL(9,I3:I99999)</f>
         <v>0</v>
       </c>
       <c r="J1" s="22" t="e">
@@ -753,7 +749,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K1" s="12">
-        <f>SUBTOTAL(9,K3:K3)</f>
+        <f>SUBTOTAL(9,K3:K99999)</f>
         <v>0</v>
       </c>
       <c r="L1" s="23">
@@ -810,7 +806,7 @@
     </row>
     <row r="3" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5"/>
@@ -843,6 +839,6 @@
   </sheetData>
   <autoFilter ref="C2:O2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/app/templates/report/mf.xlsx
+++ b/app/templates/report/mf.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E00C1A1-457E-4AB4-8756-64CE86590821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B5578C-C721-452D-8252-8FE4281DDFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fee" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fee!$C$2:$O$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fee!$C$2:$P$2</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Recurso</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>Grupo IVA</t>
+  </si>
+  <si>
+    <t>Tipo</t>
   </si>
 </sst>
 </file>
@@ -704,62 +707,64 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.77734375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.44140625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" style="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="50.88671875" style="18" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="11.88671875" style="1"/>
+    <col min="1" max="1" width="48.7109375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.42578125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" style="18" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="50.85546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.85546875" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="11.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="10"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="11" t="s">
+      <c r="D1" s="10"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="12">
-        <f>SUBTOTAL(9,G3:G99999)</f>
+      <c r="H1" s="12">
+        <f>SUBTOTAL(9,H3:H99999)</f>
         <v>0</v>
       </c>
-      <c r="H1" s="13"/>
-      <c r="I1" s="12">
-        <f>SUBTOTAL(9,I3:I99999)</f>
+      <c r="I1" s="13"/>
+      <c r="J1" s="12">
+        <f>SUBTOTAL(9,J3:J99999)</f>
         <v>0</v>
       </c>
-      <c r="J1" s="22" t="e">
-        <f>K1/I1</f>
+      <c r="K1" s="22" t="e">
+        <f>L1/J1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K1" s="12">
-        <f>SUBTOTAL(9,K3:K99999)</f>
+      <c r="L1" s="12">
+        <f>SUBTOTAL(9,L3:L99999)</f>
         <v>0</v>
       </c>
-      <c r="L1" s="23">
+      <c r="M1" s="23">
         <v>0.54</v>
       </c>
-      <c r="M1" s="17"/>
       <c r="N1" s="17"/>
-      <c r="O1" s="13"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="13"/>
     </row>
-    <row r="2" spans="1:15" s="4" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" s="4" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -770,74 +775,78 @@
         <v>5</v>
       </c>
       <c r="D2" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="I2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="J2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="K2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="19"/>
+      <c r="M2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="N2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="O2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="P2" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="26"/>
       <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="9" t="s">
-        <v>1</v>
-      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="3"/>
       <c r="F3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="7">
-        <f>G3/(1+H3)</f>
+      <c r="G3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="7">
+        <f>H3/(1+I3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="20"/>
-      <c r="K3" s="7">
-        <f>I3*J3</f>
+      <c r="K3" s="20"/>
+      <c r="L3" s="7">
+        <f>J3*K3</f>
         <v>0</v>
       </c>
-      <c r="L3" s="24">
-        <f>K3*0.21*$L$1</f>
+      <c r="M3" s="24">
+        <f>L3*0.21*$M$1</f>
         <v>0</v>
       </c>
-      <c r="M3" s="16"/>
       <c r="N3" s="16"/>
       <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="C2:O2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="C2:P2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/app/templates/report/mf.xlsx
+++ b/app/templates/report/mf.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\oimbra\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B5578C-C721-452D-8252-8FE4281DDFC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64A460B-10A1-4D43-B39A-CAEE58FEE247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fee" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fee!$C$2:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fee!$C$2:$Q$2</definedName>
   </definedNames>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -707,64 +707,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.42578125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20" style="18" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="50.85546875" style="18" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.85546875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="11.85546875" style="1"/>
+    <col min="1" max="1" width="48.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.44140625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20" style="18" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="50.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.88671875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="11.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="11" t="s">
+      <c r="E1" s="10"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12">
-        <f>SUBTOTAL(9,H3:H99999)</f>
+      <c r="I1" s="12">
+        <f>SUBTOTAL(9,I3:I99999)</f>
         <v>0</v>
       </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="12">
-        <f>SUBTOTAL(9,J3:J99999)</f>
+      <c r="J1" s="13"/>
+      <c r="K1" s="12">
+        <f>SUBTOTAL(9,K3:K99999)</f>
         <v>0</v>
       </c>
-      <c r="K1" s="22" t="e">
-        <f>L1/J1</f>
+      <c r="L1" s="22" t="e">
+        <f>M1/K1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L1" s="12">
-        <f>SUBTOTAL(9,L3:L99999)</f>
+      <c r="M1" s="12">
+        <f>SUBTOTAL(9,M3:M99999)</f>
         <v>0</v>
       </c>
-      <c r="M1" s="23">
+      <c r="N1" s="23">
         <v>0.54</v>
       </c>
-      <c r="N1" s="17"/>
       <c r="O1" s="17"/>
-      <c r="P1" s="13"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="13"/>
     </row>
-    <row r="2" spans="1:16" s="4" customFormat="1" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" s="4" customFormat="1" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>4</v>
       </c>
@@ -777,76 +778,78 @@
       <c r="D2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="14"/>
+      <c r="F2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="H2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="I2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="J2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="K2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="L2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="19"/>
+      <c r="N2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="O2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="P2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="Q2" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
       <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="5"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="9" t="s">
-        <v>1</v>
-      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="3"/>
       <c r="G3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="7">
-        <f>H3/(1+I3)</f>
+      <c r="H3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="7">
+        <f>I3/(1+J3)</f>
         <v>0</v>
       </c>
-      <c r="K3" s="20"/>
-      <c r="L3" s="7">
-        <f>J3*K3</f>
+      <c r="L3" s="20"/>
+      <c r="M3" s="7">
+        <f>K3*L3</f>
         <v>0</v>
       </c>
-      <c r="M3" s="24">
-        <f>L3*0.21*$M$1</f>
+      <c r="N3" s="24">
+        <f>M3*0.21*$N$1</f>
         <v>0</v>
       </c>
-      <c r="N3" s="16"/>
       <c r="O3" s="16"/>
       <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="C2:P2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="C2:Q2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
